--- a/Data/BS/BS_Quizzes.xlsx
+++ b/Data/BS/BS_Quizzes.xlsx
@@ -5,27 +5,26 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\BS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43471273-41DB-478F-8F78-DEC05EF07AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9861AC-11F9-4213-8E02-D8B5CF345271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="6" xr2:uid="{633C1E91-D41C-43BA-9D9E-974D9C4715DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{633C1E91-D41C-43BA-9D9E-974D9C4715DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Week 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Week 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Week 3" sheetId="4" r:id="rId4"/>
-    <sheet name="Week 4" sheetId="5" r:id="rId5"/>
-    <sheet name="Week 5" sheetId="6" r:id="rId6"/>
-    <sheet name="Week 6" sheetId="7" r:id="rId7"/>
-    <sheet name="Week 7" sheetId="8" r:id="rId8"/>
-    <sheet name="Week 8" sheetId="9" r:id="rId9"/>
-    <sheet name="Week 9" sheetId="10" r:id="rId10"/>
-    <sheet name="Week 10" sheetId="11" r:id="rId11"/>
-    <sheet name="Week 11" sheetId="12" r:id="rId12"/>
-    <sheet name="Week 12" sheetId="13" r:id="rId13"/>
+    <sheet name="Week 1" sheetId="2" r:id="rId1"/>
+    <sheet name="Week 2" sheetId="3" r:id="rId2"/>
+    <sheet name="Week 3" sheetId="4" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="7" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="8" r:id="rId7"/>
+    <sheet name="Week 8" sheetId="9" r:id="rId8"/>
+    <sheet name="Week 9" sheetId="10" r:id="rId9"/>
+    <sheet name="Week 10" sheetId="11" r:id="rId10"/>
+    <sheet name="Week 11" sheetId="12" r:id="rId11"/>
+    <sheet name="Week 12" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="1024">
   <si>
     <t>30-40</t>
   </si>
@@ -482,30 +481,9 @@
     <t>20</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20-30 </t>
-  </si>
-  <si>
-    <t>10-20 </t>
-  </si>
-  <si>
-    <t>0-10 </t>
-  </si>
-  <si>
-    <t>Class interval </t>
-  </si>
-  <si>
-    <t>Given the following grouped data, what is the mean? </t>
-  </si>
-  <si>
     <t>Divide the total sum of all frequencies by the number of classes</t>
   </si>
   <si>
@@ -734,33 +712,12 @@
     <t>What is the unit of measurement for variance?</t>
   </si>
   <si>
-    <t>5.63</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>6.22</t>
-  </si>
-  <si>
-    <t>4.97</t>
-  </si>
-  <si>
-    <t>Calculate the standard deviation of calls received. </t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Calls (x)</t>
-  </si>
-  <si>
-    <t>The following is a frequency distribution of the number of calls received at a call centre during different hours of the day:</t>
-  </si>
-  <si>
     <t>s = \sqrt{\frac{\sum{(x - \bar{x})^2}}{n}}</t>
   </si>
   <si>
@@ -857,24 +814,12 @@
     <t>Standard deviation = 1.50, variation exceeds 2 items</t>
   </si>
   <si>
-    <t>Standard deviation = 1.13. Variation is acceptable</t>
-  </si>
-  <si>
     <t>Standard deviation = 2.00, variation exceeds two items</t>
   </si>
   <si>
     <t>Standard deviation = 1.25, variation is acceptable</t>
   </si>
   <si>
-    <t>Calculate the standard deviation. Does the variation exceed 2 items?</t>
-  </si>
-  <si>
-    <t>12        14        15       13       16        15        14        18        13        15 </t>
-  </si>
-  <si>
-    <t>The weekly production of a company over 10 weeks is </t>
-  </si>
-  <si>
     <t>Mean of the dataset</t>
   </si>
   <si>
@@ -983,9 +928,6 @@
     <t>What does the standard deviation measure in a dataset?</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>Volume, Uniqueness, Clarity, Ambiguity</t>
   </si>
   <si>
@@ -1640,9 +1582,6 @@
     <t>When is the t-distribution used instead of the normal distribution?</t>
   </si>
   <si>
-    <t xml:space="preserve">UnansweredQuestion 3 </t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -2042,18 +1981,6 @@
     <t>W = 5</t>
   </si>
   <si>
-    <t>Using the Wilcoxon Signed-Rank Test, what is the test statistic (W) for the difference between the paired scores?</t>
-  </si>
-  <si>
-    <t>After Training: [55, 60, 65, 70, 75]</t>
-  </si>
-  <si>
-    <t>Before Training: [50, 55, 60, 65, 70]</t>
-  </si>
-  <si>
-    <t>A company wants to evaluate the impact of a new training program on employee performance. Employee performance scores before and after the training are given as follows:</t>
-  </si>
-  <si>
     <t>Mann-Whitney U test</t>
   </si>
   <si>
@@ -2114,21 +2041,6 @@
     <t>The highest selling store</t>
   </si>
   <si>
-    <t>Store C: 31, 33, 34</t>
-  </si>
-  <si>
-    <t>Store B: 32, 30, 29</t>
-  </si>
-  <si>
-    <t>Store A: 30, 35, 28</t>
-  </si>
-  <si>
-    <t>Monthly Sales in Stores. Monthly sales (in thousands) for three stores are observed:</t>
-  </si>
-  <si>
-    <t>What conclusion does the Kruskal-Wallis test help draw?</t>
-  </si>
-  <si>
     <t>When the calculated value is less than the critical value</t>
   </si>
   <si>
@@ -2201,21 +2113,6 @@
     <t>Yes, Group Y has higher ranks</t>
   </si>
   <si>
-    <t>Group Y: [25, 24, 23, 26, 27]</t>
-  </si>
-  <si>
-    <t>Group X: [20, 22, 21, 19, 18]</t>
-  </si>
-  <si>
-    <t>Group B: [17, 16, 19, 13, 11]</t>
-  </si>
-  <si>
-    <t>Group A: [12, 15, 14, 10, 18]</t>
-  </si>
-  <si>
-    <t>Which group has the higher rank sum?</t>
-  </si>
-  <si>
     <t>Test not applicable</t>
   </si>
   <si>
@@ -2225,15 +2122,6 @@
     <t>Sample 1 has higher ranks</t>
   </si>
   <si>
-    <t>Sample 2: [40, 39, 37, 36, 38]</t>
-  </si>
-  <si>
-    <t>Sample 1: [35, 30, 28, 32, 31]</t>
-  </si>
-  <si>
-    <t>What is the conclusion of the Mann-Whitney U test at 5%?</t>
-  </si>
-  <si>
     <t>Sign test</t>
   </si>
   <si>
@@ -2483,24 +2371,6 @@
     <t>What is required for simple regression analysis?</t>
   </si>
   <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>In a dataset with 7 observations, the sum of squared rank differences is 35. What is the Spearman rank correlation coefficient?</t>
-  </si>
-  <si>
-    <t>Price: 3, 4, 2, 5, 1</t>
-  </si>
-  <si>
-    <t>Days to sell Home: 1, 2, 3, 4, 5</t>
-  </si>
-  <si>
-    <t>Given the following ranks, calculate the Spearman rank correlation coefficient.</t>
-  </si>
-  <si>
     <t>Ordinal</t>
   </si>
   <si>
@@ -2627,9 +2497,6 @@
     <t>What does a negative Spearman correlation coefficient indicate?</t>
   </si>
   <si>
-    <t>That’s correct</t>
-  </si>
-  <si>
     <t>There is no relationship between X and Y</t>
   </si>
   <si>
@@ -2723,9 +2590,6 @@
     <t>If the R² of a model is 0.25, what does this mean?</t>
   </si>
   <si>
-    <t>That’s incorrect</t>
-  </si>
-  <si>
     <t>a and C</t>
   </si>
   <si>
@@ -3213,6 +3077,77 @@
   </si>
   <si>
     <t>Question 3</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Given the following grouped data, what is the mean? 
+Class Interval | Frequency
+0-10                    | 2
+10-20                  | 3
+20-30                  | 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The following is a frequency distribution of the number of calls received at a call centre during different hours of the day:
+Calls (x) | Frequecy
+5               | 10
+10             | 15
+15             | 20
+20             | 25
+25             | 10
+Calculate the standard deviation of calls received. </t>
+  </si>
+  <si>
+    <t>The weekly production of a company over 10 weeks is 
+12        14        15       13       16        15        14        18        13        15 
+Calculate the standard deviation. Does the variation exceed 2 items?</t>
+  </si>
+  <si>
+    <t>Standard deviation = 1.33, variation is acceptable</t>
+  </si>
+  <si>
+    <t>A company wants to evaluate the impact of a new training program on employee performance. Employee performance scores before and after the training are given as follows:
+Before Training: [50, 55, 60, 65, 70]
+After Training: [55, 60, 65, 70, 75]
+Using the Wilcoxon Signed-Rank Test, what is the test statistic (W) for the difference between the paired scores?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What conclusion does the Kruskal-Wallis test help draw?
+Monthly Sales in Stores. Monthly sales (in thousands) for three stores are observed:
+Store A: 30, 35, 28
+Store B: 32, 30, 29
+Store C: 31, 33, 34 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the conclusion of the Mann-Whitney U test at 5%?
+Sample 1: [35, 30, 28, 32, 31]
+Sample 2: [40, 39, 37, 36, 38] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which group has the higher rank sum?
+Group A: [12, 15, 14, 10, 18]
+Group B: [17, 16, 19, 13, 11]
+Group X: [20, 22, 21, 19, 18]
+Group Y: [25, 24, 23, 26, 27] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given the following ranks, calculate the Spearman rank correlation coefficient.
+Days to sell Home: 1, 2, 3, 4, 5
+Price: 3, 4, 2, 5, 1
+In a dataset with 7 observations, the sum of squared rank differences is 35. What is the Spearman rank correlation coefficient? </t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -3350,9 +3285,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3686,531 +3629,508 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97D50F68-12C9-42FC-9810-EE8BB9ED9C37}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C7243B-E8C4-4CA9-BAB5-875DFAE93E82}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAFA706-F42F-4A29-A0A6-B9825ADF92FC}">
-  <sheetPr codeName="Sheet17"/>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="55" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="4.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>858</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>854</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>790</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>781</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>780</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>851</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>850</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>849</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>843</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>842</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>841</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>839</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>834</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>831</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>830</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>824</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>820</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>819</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>815</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>810</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4727B-5466-4F6D-9C28-551795F7B76D}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G21"/>
@@ -4241,7 +4161,7 @@
         <v>114</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>120</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4249,22 +4169,22 @@
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>956</v>
+        <v>911</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>955</v>
+        <v>910</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>954</v>
+        <v>909</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>953</v>
+        <v>908</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>952</v>
+        <v>907</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4272,22 +4192,22 @@
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>901</v>
+        <v>856</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>900</v>
+        <v>855</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>899</v>
+        <v>854</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>898</v>
+        <v>853</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>897</v>
+        <v>852</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4295,22 +4215,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>890</v>
+        <v>846</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>889</v>
+        <v>845</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>888</v>
+        <v>844</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>887</v>
+        <v>843</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>886</v>
+        <v>842</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4318,22 +4238,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>885</v>
+        <v>841</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>884</v>
+        <v>840</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>883</v>
+        <v>839</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>882</v>
+        <v>838</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>881</v>
+        <v>837</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4341,22 +4261,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>880</v>
+        <v>836</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>879</v>
+        <v>835</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>878</v>
+        <v>834</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>877</v>
+        <v>833</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>876</v>
+        <v>832</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4364,22 +4284,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>875</v>
+        <v>831</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>874</v>
+        <v>830</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>873</v>
+        <v>829</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>872</v>
+        <v>828</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>871</v>
+        <v>827</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4387,22 +4307,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>870</v>
+        <v>826</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>869</v>
+        <v>825</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>868</v>
+        <v>824</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>867</v>
+        <v>823</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>866</v>
+        <v>822</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4410,22 +4330,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>865</v>
+        <v>821</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>792</v>
+        <v>755</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>791</v>
+        <v>754</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,22 +4353,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>864</v>
+        <v>820</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>863</v>
+        <v>819</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>862</v>
+        <v>818</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>861</v>
+        <v>817</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>860</v>
+        <v>816</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4456,22 +4376,22 @@
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>951</v>
+        <v>906</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>950</v>
+        <v>905</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>949</v>
+        <v>904</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>948</v>
+        <v>903</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>947</v>
+        <v>902</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>891</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4479,22 +4399,22 @@
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>946</v>
+        <v>901</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>945</v>
+        <v>900</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>944</v>
+        <v>899</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>943</v>
+        <v>898</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>942</v>
+        <v>897</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4502,22 +4422,22 @@
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>941</v>
+        <v>896</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>940</v>
+        <v>895</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>939</v>
+        <v>894</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>938</v>
+        <v>893</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>937</v>
+        <v>892</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,22 +4445,22 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>936</v>
+        <v>891</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>935</v>
+        <v>890</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>934</v>
+        <v>889</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>933</v>
+        <v>888</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>932</v>
+        <v>887</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4548,22 +4468,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>931</v>
+        <v>886</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>930</v>
+        <v>885</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>929</v>
+        <v>884</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>928</v>
+        <v>883</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>927</v>
+        <v>882</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4571,22 +4491,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>926</v>
+        <v>881</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>925</v>
+        <v>880</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>924</v>
+        <v>879</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>923</v>
+        <v>878</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>922</v>
+        <v>877</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4594,22 +4514,22 @@
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>921</v>
+        <v>876</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>919</v>
+        <v>874</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>918</v>
+        <v>873</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>917</v>
+        <v>872</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4617,22 +4537,22 @@
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>916</v>
+        <v>871</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>915</v>
+        <v>870</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>914</v>
+        <v>869</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>913</v>
+        <v>868</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>912</v>
+        <v>867</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4640,22 +4560,22 @@
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>911</v>
+        <v>866</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>910</v>
+        <v>865</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>909</v>
+        <v>864</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>908</v>
+        <v>863</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>907</v>
+        <v>862</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4663,22 +4583,22 @@
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>906</v>
+        <v>861</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>905</v>
+        <v>860</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>904</v>
+        <v>859</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>903</v>
+        <v>858</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>902</v>
+        <v>857</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4686,22 +4606,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>896</v>
+        <v>851</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>895</v>
+        <v>850</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>894</v>
+        <v>849</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>893</v>
+        <v>848</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>892</v>
+        <v>847</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>891</v>
+        <v>1014</v>
       </c>
     </row>
   </sheetData>
@@ -4709,7 +4629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CD9BC5-E2C2-44EF-A0F7-A787CE893CDB}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G21"/>
@@ -4744,7 +4664,7 @@
         <v>114</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>120</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4752,22 +4672,22 @@
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1053</v>
+        <v>1008</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1052</v>
+        <v>1007</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1051</v>
+        <v>1006</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1050</v>
+        <v>1005</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1049</v>
+        <v>1004</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4775,22 +4695,22 @@
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1001</v>
+        <v>956</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1000</v>
+        <v>955</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>999</v>
+        <v>954</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>998</v>
+        <v>953</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>997</v>
+        <v>952</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4798,22 +4718,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>991</v>
+        <v>946</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>990</v>
+        <v>945</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>989</v>
+        <v>944</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>988</v>
+        <v>943</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>987</v>
+        <v>942</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4821,22 +4741,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>986</v>
+        <v>941</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>985</v>
+        <v>940</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>984</v>
+        <v>939</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>983</v>
+        <v>938</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>982</v>
+        <v>937</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4844,22 +4764,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>981</v>
+        <v>936</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>980</v>
+        <v>935</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>979</v>
+        <v>934</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>978</v>
+        <v>933</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>977</v>
+        <v>932</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4867,22 +4787,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>976</v>
+        <v>931</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>975</v>
+        <v>930</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>974</v>
+        <v>929</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>973</v>
+        <v>928</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>972</v>
+        <v>927</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4890,22 +4810,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>969</v>
+        <v>924</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>968</v>
+        <v>923</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>967</v>
+        <v>922</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4913,22 +4833,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>966</v>
+        <v>921</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>965</v>
+        <v>920</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>964</v>
+        <v>919</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>963</v>
+        <v>918</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>962</v>
+        <v>917</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4936,22 +4856,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>961</v>
+        <v>916</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>960</v>
+        <v>915</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>959</v>
+        <v>914</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>958</v>
+        <v>913</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>957</v>
+        <v>912</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4959,22 +4879,22 @@
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1048</v>
+        <v>1003</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1047</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1046</v>
+        <v>1001</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1045</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1044</v>
+        <v>999</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4982,22 +4902,22 @@
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1043</v>
+        <v>998</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1042</v>
+        <v>997</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1041</v>
+        <v>996</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1040</v>
+        <v>995</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1039</v>
+        <v>994</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5005,22 +4925,22 @@
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1038</v>
+        <v>993</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1037</v>
+        <v>992</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1036</v>
+        <v>991</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1035</v>
+        <v>990</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>1034</v>
+        <v>989</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5028,22 +4948,22 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1033</v>
+        <v>988</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1032</v>
+        <v>987</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1031</v>
+        <v>986</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1030</v>
+        <v>985</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1029</v>
+        <v>984</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5051,22 +4971,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1028</v>
+        <v>983</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>1027</v>
+        <v>982</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>891</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5074,22 +4994,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1026</v>
+        <v>981</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1025</v>
+        <v>980</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>1024</v>
+        <v>979</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1023</v>
+        <v>978</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1022</v>
+        <v>977</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5097,22 +5017,22 @@
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1021</v>
+        <v>976</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1020</v>
+        <v>975</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1019</v>
+        <v>974</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>1018</v>
+        <v>973</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>1017</v>
+        <v>972</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5120,22 +5040,22 @@
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1016</v>
+        <v>971</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1015</v>
+        <v>970</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1014</v>
+        <v>969</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1013</v>
+        <v>968</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1012</v>
+        <v>967</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5143,22 +5063,22 @@
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>1011</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5166,22 +5086,22 @@
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1006</v>
+        <v>961</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1005</v>
+        <v>960</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1004</v>
+        <v>959</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1003</v>
+        <v>958</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1002</v>
+        <v>957</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5189,22 +5109,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>996</v>
+        <v>951</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>995</v>
+        <v>950</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>994</v>
+        <v>949</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>993</v>
+        <v>948</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>992</v>
+        <v>947</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>891</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -5212,7 +5132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF80BFE-D0B8-4492-80A5-E94ED958B3B6}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:G21"/>
@@ -5247,7 +5167,7 @@
         <v>114</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>120</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,22 +5175,22 @@
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1053</v>
+        <v>1008</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1052</v>
+        <v>1007</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1051</v>
+        <v>1006</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1050</v>
+        <v>1005</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1049</v>
+        <v>1004</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,22 +5198,22 @@
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>1001</v>
+        <v>956</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1000</v>
+        <v>955</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>999</v>
+        <v>954</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>998</v>
+        <v>953</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>997</v>
+        <v>952</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5301,22 +5221,22 @@
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>991</v>
+        <v>946</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>990</v>
+        <v>945</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>989</v>
+        <v>944</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>988</v>
+        <v>943</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>987</v>
+        <v>942</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,22 +5244,22 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>986</v>
+        <v>941</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>985</v>
+        <v>940</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>984</v>
+        <v>939</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>983</v>
+        <v>938</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>982</v>
+        <v>937</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,22 +5267,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>981</v>
+        <v>936</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>980</v>
+        <v>935</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>979</v>
+        <v>934</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>978</v>
+        <v>933</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>977</v>
+        <v>932</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,22 +5290,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>976</v>
+        <v>931</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>975</v>
+        <v>930</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>974</v>
+        <v>929</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>973</v>
+        <v>928</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>972</v>
+        <v>927</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,22 +5313,22 @@
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>969</v>
+        <v>924</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>968</v>
+        <v>923</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>967</v>
+        <v>922</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5416,22 +5336,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>966</v>
+        <v>921</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>965</v>
+        <v>920</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>964</v>
+        <v>919</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>963</v>
+        <v>918</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>962</v>
+        <v>917</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,22 +5359,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>961</v>
+        <v>916</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>960</v>
+        <v>915</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>959</v>
+        <v>914</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>958</v>
+        <v>913</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>957</v>
+        <v>912</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5462,22 +5382,22 @@
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1048</v>
+        <v>1003</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1047</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1046</v>
+        <v>1001</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1045</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1044</v>
+        <v>999</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>859</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,22 +5405,22 @@
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1043</v>
+        <v>998</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1042</v>
+        <v>997</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1041</v>
+        <v>996</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1040</v>
+        <v>995</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1039</v>
+        <v>994</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,22 +5428,22 @@
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1038</v>
+        <v>993</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1037</v>
+        <v>992</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1036</v>
+        <v>991</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1035</v>
+        <v>990</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>1034</v>
+        <v>989</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5531,22 +5451,22 @@
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1033</v>
+        <v>988</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1032</v>
+        <v>987</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1031</v>
+        <v>986</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1030</v>
+        <v>985</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1029</v>
+        <v>984</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5554,22 +5474,22 @@
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1028</v>
+        <v>983</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>1027</v>
+        <v>982</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>891</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5577,22 +5497,22 @@
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1026</v>
+        <v>981</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1025</v>
+        <v>980</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>1024</v>
+        <v>979</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1023</v>
+        <v>978</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1022</v>
+        <v>977</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,22 +5520,22 @@
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1021</v>
+        <v>976</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1020</v>
+        <v>975</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1019</v>
+        <v>974</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>1018</v>
+        <v>973</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>1017</v>
+        <v>972</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5623,22 +5543,22 @@
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1016</v>
+        <v>971</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1015</v>
+        <v>970</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1014</v>
+        <v>969</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1013</v>
+        <v>968</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>1012</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,22 +5566,22 @@
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1011</v>
+        <v>966</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1010</v>
+        <v>965</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1009</v>
+        <v>964</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1008</v>
+        <v>963</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>1007</v>
+        <v>962</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>859</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,22 +5589,22 @@
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1006</v>
+        <v>961</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1005</v>
+        <v>960</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1004</v>
+        <v>959</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1003</v>
+        <v>958</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1002</v>
+        <v>957</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>859</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,22 +5612,22 @@
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>996</v>
+        <v>951</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>995</v>
+        <v>950</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>994</v>
+        <v>949</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>993</v>
+        <v>948</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>992</v>
+        <v>947</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>891</v>
+        <v>1014</v>
       </c>
     </row>
   </sheetData>
@@ -5716,448 +5636,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C7243B-E8C4-4CA9-BAB5-875DFAE93E82}">
-  <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="74.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C79ABA0-5440-48C0-88FF-7EE1971F0ED9}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6165,10 +5646,9 @@
     <col min="4" max="4" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="60.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -6187,124 +5667,95 @@
       <c r="F1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>143</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G3" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
@@ -6323,12 +5774,11 @@
       <c r="F6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G6" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -6347,12 +5797,11 @@
       <c r="F7" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G7" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -6371,12 +5820,11 @@
       <c r="F8" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G8" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
@@ -6395,12 +5843,11 @@
       <c r="F9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G9" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -6419,284 +5866,272 @@
       <c r="F10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G10" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1014</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E83AADC-1C87-4F3F-B72B-8AB0D1431608}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6705,14 +6140,9 @@
     <col min="4" max="4" width="62.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="63" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -6731,372 +6161,292 @@
       <c r="F1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G2" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G5" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C8" s="8">
+        <v>4.97</v>
+      </c>
+      <c r="D8" s="8">
+        <v>6.22</v>
+      </c>
+      <c r="E8" s="8">
+        <v>5.8</v>
+      </c>
+      <c r="F8" s="8">
+        <v>5.63</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>143</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
@@ -7108,76 +6458,64 @@
         <v>15</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>12</v>
@@ -7191,135 +6529,111 @@
       <c r="F17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G17" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>274</v>
+      <c r="B19" s="19" t="s">
+        <v>1017</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>271</v>
+        <v>1018</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="4"/>
+        <v>239</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1012</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8069BB32-F10E-46D3-BDF2-BC7A3FF4CD76}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7329,7 +6643,7 @@
     <col min="6" max="6" width="76.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -7348,405 +6662,468 @@
       <c r="F1" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>346</v>
+        <v>327</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -7754,10 +7131,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C22EE31-EB52-4323-B584-C5D1CA60E851}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7768,7 +7145,7 @@
     <col min="6" max="6" width="57.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -7787,405 +7164,468 @@
       <c r="F1" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>128</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>440</v>
+        <v>421</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -8193,10 +7633,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A971C810-BD2E-48CE-8488-FBBAB702C689}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8206,14 +7646,9 @@
     <col min="5" max="5" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -8233,565 +7668,478 @@
         <v>114</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>1054</v>
+        <v>1009</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="C4" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="D4" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="E4" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="F4" t="s">
-        <v>525</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>121</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="4"/>
+        <v>501</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1011</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E40FBD5-6A45-4B7E-B64F-49F47E723CDE}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8800,10 +8148,9 @@
     <col min="4" max="4" width="50" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -8822,491 +8169,479 @@
       <c r="F1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>667</v>
+      <c r="B2" s="18" t="s">
+        <v>1019</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>659</v>
+        <v>639</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>648</v>
+        <v>628</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>643</v>
+        <v>623</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>639</v>
+        <v>619</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="4"/>
+        <v>593</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1013</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476D7A42-A21B-4850-92AD-F376B8357AA8}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9315,13 +8650,9 @@
     <col min="4" max="4" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>119</v>
       </c>
@@ -9340,518 +8671,971 @@
       <c r="F1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>765</v>
+        <v>728</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>764</v>
+        <v>727</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>763</v>
+        <v>726</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>712</v>
+        <v>683</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>711</v>
+        <v>682</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>710</v>
+        <v>681</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>709</v>
+        <v>680</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>702</v>
+        <v>673</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>701</v>
+        <v>672</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>700</v>
+        <v>671</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>699</v>
+        <v>670</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>697</v>
+        <v>668</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>696</v>
+        <v>667</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>695</v>
+        <v>666</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>694</v>
+        <v>665</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>692</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>691</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>690</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C6" t="s">
+        <v>663</v>
+      </c>
+      <c r="D6" t="s">
+        <v>662</v>
+      </c>
+      <c r="E6" t="s">
+        <v>661</v>
+      </c>
+      <c r="F6" t="s">
+        <v>660</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>677</v>
+        <v>653</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>672</v>
+        <v>648</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>671</v>
+        <v>647</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>670</v>
+        <v>646</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>762</v>
+        <v>725</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>761</v>
+        <v>724</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>760</v>
+        <v>723</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>759</v>
+        <v>722</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>757</v>
+        <v>720</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>756</v>
+        <v>719</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>755</v>
+        <v>718</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>753</v>
+        <v>716</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>747</v>
+        <v>710</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>752</v>
+        <v>715</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>751</v>
+        <v>714</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>750</v>
+        <v>713</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>749</v>
+        <v>712</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>748</v>
+        <v>711</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>670</v>
+        <v>646</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>746</v>
+        <v>709</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>745</v>
+        <v>708</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>744</v>
+        <v>707</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>743</v>
+        <v>706</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>741</v>
+        <v>704</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>740</v>
+        <v>703</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>738</v>
+        <v>701</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>736</v>
+        <v>699</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>735</v>
+        <v>698</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>734</v>
+        <v>697</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>733</v>
+        <v>696</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>731</v>
+        <v>694</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>730</v>
+        <v>693</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>729</v>
+        <v>692</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="19" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C19" t="s">
+        <v>690</v>
+      </c>
+      <c r="D19" t="s">
+        <v>689</v>
+      </c>
+      <c r="E19" t="s">
+        <v>688</v>
+      </c>
+      <c r="F19" t="s">
+        <v>685</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>721</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>720</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="18" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C20" t="s">
+        <v>687</v>
+      </c>
+      <c r="D20" t="s">
+        <v>686</v>
+      </c>
+      <c r="E20" t="s">
+        <v>685</v>
+      </c>
+      <c r="F20" t="s">
+        <v>684</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>707</v>
+        <v>678</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>706</v>
+        <v>677</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>705</v>
+        <v>676</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>704</v>
+        <v>675</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="4"/>
+        <v>674</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAFA706-F42F-4A29-A0A6-B9825ADF92FC}">
+  <sheetPr codeName="Sheet17"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="55" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.73</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>1012</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
